--- a/measurements/29/Filled_2D_sections/axial/week29_axial_Batch_Allmarks.xlsx
+++ b/measurements/29/Filled_2D_sections/axial/week29_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AF27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,97 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +591,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.038370017846521</v>
+        <v>3445.238095238095</v>
       </c>
       <c r="D2" t="n">
-        <v>19.09043200713832</v>
+        <v>372.7179582346053</v>
       </c>
       <c r="E2" t="n">
-        <v>13.33906298439677</v>
+        <v>260.4293249334607</v>
       </c>
       <c r="F2" t="n">
         <v>1.431167393801885</v>
@@ -525,24 +610,57 @@
         <v>0.3116509592831732</v>
       </c>
       <c r="H2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.042410714285714</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33.97693452380952</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.700272817460315</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>1.740282012195122</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.740282012195122</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.740282012195122</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>33.97693452380952</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.103422619047619</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7.87016369047619</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.925874255952381</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.042410714285714</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.800223214285714</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.905505952380952</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>9.18316478286734</v>
+      <c r="AF2" s="2" t="n">
+        <v>3500.430839002267</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +671,76 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.197501487209994</v>
+        <v>3505.895691609977</v>
       </c>
       <c r="D3" t="n">
-        <v>17.26086632216849</v>
+        <v>336.9978662899562</v>
       </c>
       <c r="E3" t="n">
-        <v>13.40559769839775</v>
+        <v>261.728336016337</v>
       </c>
       <c r="F3" t="n">
-        <v>1.287586477716806</v>
+        <v>1.287586477716807</v>
       </c>
       <c r="G3" t="n">
         <v>0.3879310594081659</v>
       </c>
       <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.378348214285714</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.71279761904762</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.266369047619047</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>1.214557926829268</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.214557926829268</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.214557926829268</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>23.71279761904762</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.066220238095238</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7.57626488095238</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.340091765873016</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3.277529761904762</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.254464285714286</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.378348214285714</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>16.53518583861793</v>
+      <c r="AF3" s="2" t="n">
+        <v>322.8298187539691</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +751,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.117787031528852</v>
+        <v>3475.510204081632</v>
       </c>
       <c r="D4" t="n">
-        <v>17.17167475746899</v>
+        <v>335.2565071696326</v>
       </c>
       <c r="E4" t="n">
-        <v>13.48295307450178</v>
+        <v>263.2386076450348</v>
       </c>
       <c r="F4" t="n">
         <v>1.273584107471464</v>
@@ -619,24 +770,54 @@
         <v>0.3885742342639247</v>
       </c>
       <c r="H4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.214657738095238</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.95572916666666</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.700975529100528</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>1.17578125</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.17578125</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.17578125</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>22.95572916666666</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.103422619047619</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7.760416666666666</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5.43154761904762</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3.549107142857143</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.214657738095238</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>13.02753147468334</v>
+      <c r="AF4" s="2" t="n">
+        <v>254.347043077151</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +828,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.004461629982154</v>
+        <v>3432.312925170068</v>
       </c>
       <c r="D5" t="n">
-        <v>16.76020997617303</v>
+        <v>327.2231471538544</v>
       </c>
       <c r="E5" t="n">
-        <v>13.53173361464245</v>
+        <v>264.1909896192096</v>
       </c>
       <c r="F5" t="n">
         <v>1.238585568817074</v>
@@ -666,24 +847,54 @@
         <v>0.4028178482610649</v>
       </c>
       <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.575520833333333</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.08444940476191</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.48354828042328</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>1.079935213414634</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.079935213414634</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.079935213414634</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>21.08444940476191</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.127604166666666</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7.607886904761904</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5.342571924603173</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3.636532738095238</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.575520833333333</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>1.269079574154951</v>
+      <c r="AF5" s="2" t="n">
+        <v>1.269079574154952</v>
       </c>
     </row>
     <row r="6">
@@ -694,17 +905,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.943188578227247</v>
+        <v>3408.956916099773</v>
       </c>
       <c r="D6" t="n">
-        <v>16.66264896567275</v>
+        <v>325.3183845678965</v>
       </c>
       <c r="E6" t="n">
-        <v>13.87911506106214</v>
+        <v>270.9731988112131</v>
       </c>
       <c r="F6" t="n">
         <v>1.20055557521962</v>
@@ -713,24 +924,51 @@
         <v>0.4047754482177888</v>
       </c>
       <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.290550595238095</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.61197916666666</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.319568452380952</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>1.055735518292683</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.055735518292683</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.055735518292683</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>20.61197916666666</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.908110119047619</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7.717633928571428</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.466889880952381</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.290550595238095</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.4284825772903927</v>
+      <c r="AF6" s="2" t="n">
+        <v>0.4284825772903928</v>
       </c>
     </row>
     <row r="7">
@@ -741,43 +979,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.870315288518739</v>
+        <v>3381.179138321995</v>
       </c>
       <c r="D7" t="n">
-        <v>16.814908498671</v>
+        <v>328.2910706883385</v>
       </c>
       <c r="E7" t="n">
-        <v>13.68399313019543</v>
+        <v>267.1636753990537</v>
       </c>
       <c r="F7" t="n">
         <v>1.228801296426173</v>
       </c>
       <c r="G7" t="n">
-        <v>0.394239290042166</v>
+        <v>0.3942392900421661</v>
       </c>
       <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.056175595238095</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20.30691964285714</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.078218005952381</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>1.040110518292683</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.040110518292683</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.040110518292683</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>20.30691964285714</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.930431547619047</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8.245907738095237</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.911458333333333</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.705357142857143</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.056175595238095</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>1.15</v>
+      <c r="AF7" s="2" t="n">
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1056,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.715050565139798</v>
+        <v>3321.995464852607</v>
       </c>
       <c r="D8" t="n">
-        <v>16.74245575579202</v>
+        <v>326.8765171368917</v>
       </c>
       <c r="E8" t="n">
-        <v>13.66133625042148</v>
+        <v>266.7213267939431</v>
       </c>
       <c r="F8" t="n">
         <v>1.225535734491235</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3906982405204583</v>
+        <v>0.3906982405204585</v>
       </c>
       <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.604166666666667</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.59449404761905</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.020089285714286</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>1.003620426829268</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.003620426829268</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.003620426829268</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>19.59449404761905</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.859747023809524</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9.546130952380953</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6.180059523809524</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.061755952380952</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.604166666666667</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>1.119240663109756</v>
+      <c r="AF8" s="2" t="n">
+        <v>1.759765625</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1133,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.662105889351578</v>
+        <v>3301.814058956916</v>
       </c>
       <c r="D9" t="n">
-        <v>17.71662952260273</v>
+        <v>345.8961002031962</v>
       </c>
       <c r="E9" t="n">
-        <v>13.75644587598196</v>
+        <v>268.5782290072668</v>
       </c>
       <c r="F9" t="n">
         <v>1.287878401319853</v>
@@ -854,24 +1152,54 @@
         <v>0.3467936568200422</v>
       </c>
       <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.453497023809524</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19.70982142857143</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.642166241496598</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19.70982142857143</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.967633928571428</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10.43712797619048</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.028459821428571</v>
+      </c>
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.5345846036585366</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.00952743902439</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7720560213414633</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="V9" t="n">
+        <v>3.218005952380952</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.453497023809524</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.191129954268292</v>
+      <c r="AF9" s="2" t="n">
+        <v>23.25539434523809</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1210,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.763533610945865</v>
+        <v>3340.47619047619</v>
       </c>
       <c r="D10" t="n">
-        <v>18.1162582199748</v>
+        <v>353.6983747709365</v>
       </c>
       <c r="E10" t="n">
-        <v>13.75991259842384</v>
+        <v>268.645912635894</v>
       </c>
       <c r="F10" t="n">
-        <v>1.316596896265893</v>
+        <v>1.316596896265894</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3355460387300491</v>
+        <v>0.3355460387300492</v>
       </c>
       <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.338169642857143</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19.73400297619047</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.480335884353741</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19.73400297619047</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.930431547619047</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10.37946428571428</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6.919177827380952</v>
+      </c>
+      <c r="U10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.5316310975609756</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.010766006097561</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.7711985518292683</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="V10" t="n">
+        <v>2.613467261904762</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.338169642857143</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>1.155185308689024</v>
+      <c r="AF10" s="2" t="n">
+        <v>5.947960014728987</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1287,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9.134741225461035</v>
+        <v>3481.972789115646</v>
       </c>
       <c r="D11" t="n">
-        <v>18.28280521602165</v>
+        <v>356.950006598518</v>
       </c>
       <c r="E11" t="n">
-        <v>12.87391498612195</v>
+        <v>251.3478640147618</v>
       </c>
       <c r="F11" t="n">
         <v>1.42014338573235</v>
@@ -948,16 +1306,57 @@
         <v>0.3434159390022702</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5245807926829269</v>
+        <v>2.100074404761905</v>
       </c>
       <c r="J11" t="n">
-        <v>1.00828887195122</v>
+        <v>19.68563988095238</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7664348323170732</v>
+        <v>6.796874999999999</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>19.68563988095238</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.930431547619047</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10.24181547619048</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7.924107142857143</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.100074404761905</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.195684523809524</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.447451636904762</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1367,76 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.375669244497324</v>
+        <v>3573.809523809523</v>
       </c>
       <c r="D12" t="n">
-        <v>16.10932479544384</v>
+        <v>314.5153888634273</v>
       </c>
       <c r="E12" t="n">
-        <v>12.8310525824384</v>
+        <v>250.5110266095116</v>
       </c>
       <c r="F12" t="n">
         <v>1.255495189653602</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4540016865926693</v>
+        <v>0.4540016865926692</v>
       </c>
       <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.954985119047619</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20.60825892857143</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.682870370370371</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>1.055544969512195</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.055544969512195</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.055544969512195</v>
+      <c r="M12" t="n">
+        <v>20.60825892857143</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8.681175595238095</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6.179315476190476</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.930431547619047</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.954985119047619</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.138020833333333</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.349330357142857</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>23.25539434523809</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1447,76 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.529149315883403</v>
+        <v>3632.312925170068</v>
       </c>
       <c r="D13" t="n">
-        <v>15.23617870051686</v>
+        <v>297.4682508196149</v>
       </c>
       <c r="E13" t="n">
-        <v>12.62654582465567</v>
+        <v>246.5182756242298</v>
       </c>
       <c r="F13" t="n">
         <v>1.206678288116248</v>
       </c>
       <c r="G13" t="n">
-        <v>0.515836276257793</v>
+        <v>0.5158362762577933</v>
       </c>
       <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.179315476190476</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20.17113095238095</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.259300595238096</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>1.033155487804878</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.033155487804878</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.033155487804878</v>
+      <c r="M13" t="n">
+        <v>20.17113095238095</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.382440476190476</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.714657738095238</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.179315476190476</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.892485119047619</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.752542162698413</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>3.95</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1527,76 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.544913741820345</v>
+        <v>3638.321995464853</v>
       </c>
       <c r="D14" t="n">
-        <v>15.47762983892022</v>
+        <v>302.1822968551091</v>
       </c>
       <c r="E14" t="n">
-        <v>12.6324639349449</v>
+        <v>246.6338196822575</v>
       </c>
       <c r="F14" t="n">
         <v>1.225226521019768</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5006946606812648</v>
+        <v>0.5006946606812649</v>
       </c>
       <c r="H14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.320684523809524</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21.46763392857143</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.428436147186146</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
-        <v>1.099561737804878</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.099561737804878</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.099561737804878</v>
+      <c r="M14" t="n">
+        <v>21.46763392857143</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.836309523809524</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.270833333333333</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.320684523809524</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.290550595238095</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.97890093537415</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>5.395378637566137</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1607,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.564544913741821</v>
+        <v>3645.804988662131</v>
       </c>
       <c r="D15" t="n">
-        <v>15.50620474466463</v>
+        <v>302.7401878720238</v>
       </c>
       <c r="E15" t="n">
-        <v>12.5693959433858</v>
+        <v>245.4024922280084</v>
       </c>
       <c r="F15" t="n">
         <v>1.233647568626735</v>
       </c>
       <c r="G15" t="n">
-        <v>0.499876990706549</v>
+        <v>0.4998769907065489</v>
       </c>
       <c r="H15" t="n">
+        <v>9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.326264880952381</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22.07961309523809</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.897900132275132</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="n">
-        <v>1.130907012195122</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.130907012195122</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.130907012195122</v>
+      <c r="M15" t="n">
+        <v>22.07961309523809</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.884672619047619</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.324776785714286</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.326264880952381</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.404017857142857</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.132006448412698</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>4.719328703703703</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1684,76 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.566032123735871</v>
+        <v>3646.371882086168</v>
       </c>
       <c r="D16" t="n">
-        <v>15.50865608599128</v>
+        <v>302.788047393163</v>
       </c>
       <c r="E16" t="n">
-        <v>12.56347787380219</v>
+        <v>245.2869489647093</v>
       </c>
       <c r="F16" t="n">
         <v>1.23442379902865</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4997966815915829</v>
+        <v>0.499796681591583</v>
       </c>
       <c r="H16" t="n">
+        <v>13</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.084449404761905</v>
+      </c>
+      <c r="J16" t="n">
+        <v>23.64769345238095</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.223042582417583</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>1.211223323170732</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.211223323170732</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.211223323170732</v>
+      <c r="M16" t="n">
+        <v>23.64769345238095</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.306919642857142</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.570777529761904</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.084449404761905</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.418154761904762</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.62109375</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>3.847888764880952</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1764,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.53718024985128</v>
+        <v>3635.374149659864</v>
       </c>
       <c r="D17" t="n">
-        <v>15.68949055090183</v>
+        <v>306.3186250414167</v>
       </c>
       <c r="E17" t="n">
-        <v>12.56939592884808</v>
+        <v>245.4024919441768</v>
       </c>
       <c r="F17" t="n">
         <v>1.248229480534765</v>
@@ -1182,16 +1783,57 @@
         <v>0.4868690536876929</v>
       </c>
       <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.088169642857143</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24.88653273809524</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.548146081349207</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>1.274676067073171</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.274676067073171</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.274676067073171</v>
+      <c r="M17" t="n">
+        <v>24.88653273809524</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5.327380952380952</v>
+      </c>
+      <c r="P17" t="n">
+        <v>5.139508928571428</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.064360119047619</v>
+      </c>
+      <c r="U17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.088169642857143</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.894996279761904</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>3.976089015151515</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1844,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.484830458060678</v>
+        <v>3615.419501133787</v>
       </c>
       <c r="D18" t="n">
-        <v>15.6086683912975</v>
+        <v>304.7406685919989</v>
       </c>
       <c r="E18" t="n">
-        <v>12.50040990259589</v>
+        <v>244.0556219078246</v>
       </c>
       <c r="F18" t="n">
         <v>1.248652525230884</v>
@@ -1221,16 +1863,57 @@
         <v>0.4892239706751338</v>
       </c>
       <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.142113095238095</v>
+      </c>
+      <c r="J18" t="n">
+        <v>25.71986607142857</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.468936011904762</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>1.317358993902439</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.317358993902439</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.317358993902439</v>
+      <c r="M18" t="n">
+        <v>25.71986607142857</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5.29203869047619</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.910714285714286</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="U18" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.142113095238095</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.380952380952381</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.736886160714286</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>8.426339285714285</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +1924,76 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.339381320642476</v>
+        <v>3559.977324263038</v>
       </c>
       <c r="D19" t="n">
-        <v>15.73235300110608</v>
+        <v>307.1554633549281</v>
       </c>
       <c r="E19" t="n">
-        <v>12.34815040158063</v>
+        <v>241.0829364118122</v>
       </c>
       <c r="F19" t="n">
-        <v>1.274065547427431</v>
+        <v>1.274065547427432</v>
       </c>
       <c r="G19" t="n">
         <v>0.474177133274123</v>
       </c>
       <c r="H19" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.147693452380952</v>
+      </c>
+      <c r="J19" t="n">
+        <v>27.97991071428571</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.452409569597069</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>1.43311737804878</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.43311737804878</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.43311737804878</v>
+      <c r="M19" t="n">
+        <v>27.97991071428571</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5.327380952380952</v>
+      </c>
+      <c r="P19" t="n">
+        <v>5.079985119047619</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.9453125</v>
+      </c>
+      <c r="U19" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.147693452380952</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.691592261904762</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.727637235449735</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>6.003728693181818</v>
       </c>
     </row>
     <row r="20">
@@ -1280,35 +2004,76 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.248661511005354</v>
+        <v>3525.396825396825</v>
       </c>
       <c r="D20" t="n">
-        <v>15.56825733475569</v>
+        <v>303.9516908214206</v>
       </c>
       <c r="E20" t="n">
-        <v>12.35406844790389</v>
+        <v>241.1984792209807</v>
       </c>
       <c r="F20" t="n">
         <v>1.260172501100004</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4795222306653497</v>
+        <v>0.4795222306653496</v>
       </c>
       <c r="H20" t="n">
+        <v>11</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.240699404761905</v>
+      </c>
+      <c r="J20" t="n">
+        <v>27.66183035714285</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.870975378787879</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>1.416825457317073</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.416825457317073</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.416825457317073</v>
+      <c r="M20" t="n">
+        <v>27.66183035714285</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.92001488095238</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.674479166666666</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.558407738095238</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.240699404761905</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.672991071428571</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.823713860544217</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>4.6</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +2084,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.025877453896491</v>
+        <v>3440.47619047619</v>
       </c>
       <c r="D21" t="n">
-        <v>15.64806408707689</v>
+        <v>305.5098226524535</v>
       </c>
       <c r="E21" t="n">
-        <v>12.18160337936587</v>
+        <v>237.8313040733337</v>
       </c>
       <c r="F21" t="n">
         <v>1.284565225098591</v>
@@ -1338,16 +2103,57 @@
         <v>0.4632101471265933</v>
       </c>
       <c r="H21" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.657366071428571</v>
+      </c>
+      <c r="J21" t="n">
+        <v>29.51264880952381</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.63876488095238</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>1.511623475609756</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.511623475609756</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.511623475609756</v>
+      <c r="M21" t="n">
+        <v>29.51264880952381</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.906994047619047</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.069940476190476</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.489583333333333</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.657366071428571</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.312872023809524</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.782738095238095</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>3.294038318452381</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2163,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>2.213807397959184</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2185,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>1.378348214285714</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2202,70 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>1.440352182539683</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>3.044239831349206</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>2.096066906218506</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/29/Filled_2D_sections/axial/week29_axial_Batch_Allmarks.xlsx
+++ b/measurements/29/Filled_2D_sections/axial/week29_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2271,4 +2477,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week29_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3500.430839002267</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115.0649903393976</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3301.814058956916</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3646.371882086168</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>322.8298187539691</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21.77709978953422</v>
+      </c>
+      <c r="E11" t="n">
+        <v>297.4682508196149</v>
+      </c>
+      <c r="F11" t="n">
+        <v>372.7179582346053</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.269079574154952</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06107141678027111</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.20055557521962</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.431167393801885</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4284825772903928</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.06486065592628609</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3116509592831732</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5158362762577933</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0133.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0137.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>9</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>11</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>8</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>8</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>9</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>11</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.904979624148524</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.190974832912761</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.583347481568501</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>20</v>
+      </c>
+      <c r="C48" t="n">
+        <v>23.25539434523809</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.957929190429376</v>
+      </c>
+      <c r="E48" t="n">
+        <v>19.59449404761905</v>
+      </c>
+      <c r="F48" t="n">
+        <v>33.97693452380952</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>79</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.516029987944545</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.686107818546577</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.489583333333333</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10.43712797619048</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>92</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.119726966873706</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6975225394810834</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.084449404761905</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.800223214285714</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>